--- a/data/trending_integrated_20260918_15.xlsx
+++ b/data/trending_integrated_20260918_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26550</v>
+        <v>26450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.92%</t>
+          <t>'+40.10%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G2" t="n">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21600</v>
+        <v>18880</v>
       </c>
       <c r="K2" t="n">
-        <v>22250</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>28050</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>21700</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>465888642700</v>
+        <v>469959000000</v>
       </c>
       <c r="P2" t="n">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-213000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>181000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>업황 실적 성장성 언급하며 '미래 SK하이닉스' 비유, 프로그램 매수세 유입.</t>
+          <t>4만원-5만원대 움직임 언급 및 5~6만원대 재진입 신호 기대. 통신주 하락 속에서 성호전자 미래 성장성 및 프로그램 폭풍 매수에 대한 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['성장성', '프로그램 매수', '미래 가치']</t>
+          <t>['성장성', '프로그램매수', '통신주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7990</v>
+        <v>6460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.82%</t>
+          <t>'+14.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>433</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7020</v>
+        <v>5620</v>
       </c>
       <c r="K3" t="n">
-        <v>7180</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8890</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7150</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.59</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>159570851525</v>
+        <v>95176000000</v>
       </c>
       <c r="P3" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>627000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
+          <t>전환사채 발행 가능성 언급, 외국인 순매수 기반 박스권 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공시', '외국인 매수', '급락 우려']</t>
+          <t>['전환사채', '외국인 순매수', '박스권 돌파']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18140</v>
+        <v>17520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.46%</t>
+          <t>'+14.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.27</v>
+        <v>0.38</v>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>191</v>
       </c>
       <c r="F4" t="n">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>2712</v>
+        <v>428</v>
       </c>
       <c r="H4" t="n">
-        <v>4.61</v>
+        <v>0.98</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16130</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>16360</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18990</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>16170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.88</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>876373694855</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1369000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>147000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
+          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대한광통신', '매물대', '공매도']</t>
+          <t>['단타', '락업해제', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31375</v>
+        <v>18130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.87%</t>
+          <t>'+11.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>158</v>
+        <v>503</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="G5" t="n">
-        <v>262</v>
+        <v>2744</v>
       </c>
       <c r="H5" t="n">
-        <v>11.44</v>
+        <v>4.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>28300</v>
+        <v>16230</v>
       </c>
       <c r="K5" t="n">
-        <v>28850</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>32050</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>28550</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46</v>
+        <v>4.88</v>
       </c>
       <c r="O5" t="n">
-        <v>228257899850</v>
+        <v>884963000000</v>
       </c>
       <c r="P5" t="n">
-        <v>75900</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 및 저평가 해소 기대.</t>
+          <t>수익률 520% 돌파 및 18000/20000원 돌파 기대감. 코닝, 어플라이드옵토 등 관련주 상승 언급과 함께 숏커버링 발생 가능성이 제기되며 2차 매물대 돌파 및 추석전 25층 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가온전선', '저평가']</t>
+          <t>['숏커버링', '매물대', '수익률']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6420</v>
+        <v>31250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.18%</t>
+          <t>'+11.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>11.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5880</v>
+        <v>28100</v>
       </c>
       <c r="K6" t="n">
-        <v>5950</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5840</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>11.46</v>
       </c>
       <c r="O6" t="n">
-        <v>94194335165</v>
+        <v>231541000000</v>
       </c>
       <c r="P6" t="n">
-        <v>11760</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>728000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>전환사채 발행 가능성 언급, 외국인 순매수 기반 박스권 돌파 및 추가 상승 전망.</t>
+          <t>가온전선과의 비교 및 저평가 해소 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['전환사채', '외국인 순매수', '박스권 돌파']</t>
+          <t>['가온전선', '저평가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,130 +1016,130 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12540</v>
+        <v>8020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.29%</t>
+          <t>'+10.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>794</v>
+        <v>444</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11580</v>
+        <v>7280</v>
       </c>
       <c r="K7" t="n">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13820</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>12100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.699999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="O7" t="n">
-        <v>128306456645</v>
+        <v>160264000000</v>
       </c>
       <c r="P7" t="n">
-        <v>21150</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8140</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>276000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>개인 투자자들의 손실 경험과 외인/기관 동시 매수에 대한 엇갈린 시각.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인', '기관', '손실']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>12540</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.78%</t>
+          <t>'+8.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="G8" t="n">
-        <v>218</v>
+        <v>808</v>
       </c>
       <c r="H8" t="n">
-        <v>2.83</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,222 +1147,222 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12860</v>
+        <v>11510</v>
       </c>
       <c r="K8" t="n">
-        <v>13020</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>14230</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>155861352185</v>
+        <v>129225000000</v>
       </c>
       <c r="P8" t="n">
-        <v>20300</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2885</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
+          <t>양극단 의견 속에서 일부 손실 경험 후 매도. 셀그램 관련 뉴스 기대감 및 외인/기관 동시 매수 언급이 있으나, 주가 상승에 대한 불확실성도 공존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
+          <t>['셀그램', '외인', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14120</v>
+        <v>13890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.85%</t>
+          <t>'+8.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>142</v>
+        <v>224</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>2.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13340</v>
+        <v>12770</v>
       </c>
       <c r="K9" t="n">
-        <v>13480</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16330</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>13210</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>209353622685</v>
+        <v>157185000000</v>
       </c>
       <c r="P9" t="n">
-        <v>25700</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-108000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 의혹과 함께 하락 및 조정 가능성 언급, 일부 긍정적 기대감 존재.</t>
+          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '하락 조정', '기대감']</t>
+          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1837000</v>
+        <v>4125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+7.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>247</v>
       </c>
       <c r="F10" t="n">
-        <v>485</v>
+        <v>137</v>
       </c>
       <c r="G10" t="n">
-        <v>2560</v>
+        <v>916</v>
       </c>
       <c r="H10" t="n">
-        <v>50.1</v>
+        <v>0.55</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1745000</v>
+        <v>3840</v>
       </c>
       <c r="K10" t="n">
-        <v>1810000</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1852000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1805000</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>50.2</v>
+        <v>0.95</v>
       </c>
       <c r="O10" t="n">
-        <v>4820804257500</v>
+        <v>42854000000</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>483000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>200만원 목표 설정, 외인 쌍끌이 매수와 자사주 매입으로 인한 상승 기대감.</t>
+          <t>미투온 계열사 미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재 언급. 스테이블코인 테마 편입 가능성과 함께 시총 1500억 기준 매수 기회 언급. 주포 물량 넘김 경고도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외인 쌍끌이', '목표가']</t>
+          <t>['STO', '코인', '스테이블코인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1399,20 +1399,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+7.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1423,34 +1423,34 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13330</v>
+        <v>12910</v>
       </c>
       <c r="K11" t="n">
-        <v>13600</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>13210</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>73382739810</v>
+        <v>74416000000</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>298000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>260250</v>
+        <v>1847000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+5.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>431</v>
+        <v>490</v>
       </c>
       <c r="G12" t="n">
-        <v>1914</v>
+        <v>2478</v>
       </c>
       <c r="H12" t="n">
-        <v>46.48</v>
+        <v>50.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>252500</v>
+        <v>1757000</v>
       </c>
       <c r="K12" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>262000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>46.52</v>
+        <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2749519617500</v>
+        <v>4983385000000</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1533000</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>874000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자 관련 내용은 정치적 논쟁에 치우쳐 투자 분석 정보 부재.</t>
+          <t>185/200/220 등 구체적인 목표 주가 언급과 함께 자사주 매입 및 쌍끌이 매수세 확인. 다음 주 전망 및 200만/400만원 목표 조정에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '이재명']</t>
+          <t>['자사주', '목표주가', '매수세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10930</v>
+        <v>52400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>521</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5</v>
+        <v>38.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10610</v>
+        <v>50200</v>
       </c>
       <c r="K13" t="n">
-        <v>10730</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>12390</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>10510</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12.6</v>
+        <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>118959436540</v>
+        <v>255341000000</v>
       </c>
       <c r="P13" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>52000~53000원 돌파 기대감 및 외인/기관의 매수세 언급. 4분기 예상 수주액 5조원 이상 전망치가 제시되었으며, 공매도 누르고 개인 털어내는 작업으로 해석.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['수주', '외인', '기관']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10515</v>
+        <v>86400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>132</v>
+        <v>313</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="G14" t="n">
-        <v>219</v>
+        <v>1363</v>
       </c>
       <c r="H14" t="n">
-        <v>18.13</v>
+        <v>23.23</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10250</v>
+        <v>84100</v>
       </c>
       <c r="K14" t="n">
-        <v>10280</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11500</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>10230</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18.42</v>
+        <v>23.27</v>
       </c>
       <c r="O14" t="n">
-        <v>210719873950</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 차익 실현 매도 의견 혼재.</t>
+          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인', '차익 실현']</t>
+          <t>['원전', '대미 투자', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52200</v>
+        <v>260000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>180</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>433</v>
       </c>
       <c r="G15" t="n">
-        <v>506</v>
+        <v>1957</v>
       </c>
       <c r="H15" t="n">
-        <v>38.54</v>
+        <v>46.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51100</v>
+        <v>253500</v>
       </c>
       <c r="K15" t="n">
-        <v>51600</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>55200</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>51500</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>38.62</v>
+        <v>46.52</v>
       </c>
       <c r="O15" t="n">
-        <v>252997741800</v>
+        <v>2814732000000</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4분기 수주 예상액 기반 긍정적 전망 제시, 단기 개인 물량 차익 실현 관측.</t>
+          <t>대통령 기자회견 관련 내용으로, 종목 분석과는 무관한 정치적 언급이 주를 이룸. ETF 상폐에 대한 언급도 있으나 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '외인 기관', '개인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18885</v>
+        <v>14200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.14%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>-0.75</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>500</v>
+        <v>154</v>
       </c>
       <c r="H16" t="n">
-        <v>10.74</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18490</v>
+        <v>13910</v>
       </c>
       <c r="K16" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>18760</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>10.85</v>
+        <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>135730457920</v>
+        <v>211789000000</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 호소 및 중동 전쟁 관련 수혜 기대.</t>
+          <t>개잡주로 평가하며 대광으로 이동 권유. 주가 조작 의혹 제기 및 하락 조정 예상. 13000원, 18000원 돌파 예측은 있었으나, 매도 후 후발주 가능성도 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '중동 전쟁', '수주']</t>
+          <t>['주가조작', '후발주', '하락조정']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17540</v>
+        <v>17460</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.27</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H17" t="n">
         <v>0.97</v>
@@ -1975,31 +1975,31 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17250</v>
+        <v>17120</v>
       </c>
       <c r="K17" t="n">
-        <v>17920</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>18440</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>17450</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>87129237365</v>
+        <v>88473000000</v>
       </c>
       <c r="P17" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18180</v>
+        <v>18940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.39%</t>
+          <t>'+1.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.38</v>
+        <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="H18" t="n">
-        <v>0.98</v>
+        <v>10.74</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17930</v>
+        <v>18610</v>
       </c>
       <c r="K18" t="n">
-        <v>18400</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>17260</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>10.85</v>
       </c>
       <c r="O18" t="n">
-        <v>87300754965</v>
+        <v>137804000000</v>
       </c>
       <c r="P18" t="n">
-        <v>21100</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>락업 해제 및 주포의 움직임에 대한 경계와 단기 매매 선호 의견.</t>
+          <t>미국 증시 및 중동 전쟁 관련 이슈 속에서 대차해지 운동 동참 독려. 5조원대 투르크 수자원 시장 건 수주 관련 언급이 있으나, 주가 하락에 대한 불만도 제기됨.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['락업 해제', '주포', '매도']</t>
+          <t>['대차해지', '수주', '중동']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,67 +2120,67 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4105</v>
+        <v>10125</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'-0.25%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="H19" t="n">
-        <v>0.73</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4095</v>
+        <v>10150</v>
       </c>
       <c r="K19" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4095</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.87</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>74525374511</v>
+        <v>37141000000</v>
       </c>
       <c r="P19" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13380</v>
+        <v>10560</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="E20" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G20" t="n">
-        <v>428</v>
+        <v>225</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>18.13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13360</v>
+        <v>10590</v>
       </c>
       <c r="K20" t="n">
-        <v>13450</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>13280</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>18.42</v>
       </c>
       <c r="O20" t="n">
-        <v>42586792770</v>
+        <v>211885000000</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>주가 조작 의혹 제기 및 차익 실현 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['주가 조작', '외인', '차익 실현']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>85300</v>
+        <v>10920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-1.44%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>1346</v>
+        <v>215</v>
       </c>
       <c r="H21" t="n">
-        <v>23.23</v>
+        <v>12.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>85400</v>
+        <v>11080</v>
       </c>
       <c r="K21" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>87800</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>85100</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>23.27</v>
+        <v>12.6</v>
       </c>
       <c r="O21" t="n">
-        <v>132069501100</v>
+        <v>119810000000</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-476000</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '대미 투자', '수주']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10120</v>
+        <v>13360</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.62%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="G22" t="n">
-        <v>233</v>
+        <v>430</v>
       </c>
       <c r="H22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10500</v>
+        <v>13740</v>
       </c>
       <c r="K22" t="n">
-        <v>10650</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>36758082810</v>
+        <v>42807000000</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-114000</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4095</v>
+        <v>4115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-11.65%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>94</v>
       </c>
       <c r="F23" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>909</v>
+        <v>227</v>
       </c>
       <c r="H23" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4635</v>
+        <v>4425</v>
       </c>
       <c r="K23" t="n">
-        <v>4465</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>4535</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4065</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="O23" t="n">
-        <v>41987696494</v>
+        <v>76062000000</v>
       </c>
       <c r="P23" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1738</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-108000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 코인 관련 호재에도 불구하고 하락세, 주포 매도 관측.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['STO', '코인', '주포 매도']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2595,20 +2595,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-53.49%</t>
+          <t>'-64.29%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.02</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F24" t="n">
         <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H24" t="n">
         <v>3.69</v>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>3.71</v>
       </c>
       <c r="O24" t="n">
-        <v>226701565</v>
+        <v>227000000</v>
       </c>
       <c r="P24" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>K-OTC 거래 기반 보유 의견과 함께 대주주 관련 논란 및 급락으로 인한 부정적 전망.</t>
+          <t>K-OTC 거래 및 대주주 변경 관련 언급이 있으나, 회사의 신뢰성에 대한 의문과 함께 주가 하락 및 장외 거래 가능성에 대한 부정적인 의견이 지배적. '10원도 비싸다'는 의견도 있음.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['K-OTC', '대주주', '급락']</t>
+          <t>['K-OTC', '대주주', '장외거래']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260918_15.xlsx
+++ b/data/trending_integrated_20260918_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26450</v>
+        <v>26550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+40.10%</t>
+          <t>'+22.92%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F2" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G2" t="n">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>18880</v>
+        <v>21600</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>28050</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>469959000000</v>
+        <v>475648847075</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>59600</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-213000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>181000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6460</v>
+        <v>8030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.95%</t>
+          <t>'+14.39%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.02</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>445</v>
       </c>
       <c r="H3" t="n">
-        <v>2.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5620</v>
+        <v>7020</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7180</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8890</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>7150</v>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>95176000000</v>
+        <v>161168879530</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>627000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>전환사채 발행 가능성 언급, 외국인 순매수 기반 박스권 돌파 및 추가 상승 전망.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전환사채', '외국인 순매수', '박스권 돌파']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17520</v>
+        <v>18140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.06%</t>
+          <t>'+12.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>191</v>
+        <v>515</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="G4" t="n">
-        <v>428</v>
+        <v>2776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.98</v>
+        <v>4.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>16130</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>18990</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>16170</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>893245605160</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1369000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
+          <t>수익률 520% 돌파 및 18000/20000원 돌파 기대감. 코닝, 어플라이드옵토 등 관련주 상승 언급과 함께 숏커버링 발생 가능성이 제기되며 2차 매물대 돌파 및 추석전 25층 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['단타', '락업해제', '주포']</t>
+          <t>['숏커버링', '매물대', '수익률']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18130</v>
+        <v>31300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.71%</t>
+          <t>'+10.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>503</v>
+        <v>166</v>
       </c>
       <c r="F5" t="n">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>2744</v>
+        <v>263</v>
       </c>
       <c r="H5" t="n">
-        <v>4.61</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16230</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>4.88</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>884963000000</v>
+        <v>234060480650</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>수익률 520% 돌파 및 18000/20000원 돌파 기대감. 코닝, 어플라이드옵토 등 관련주 상승 언급과 함께 숏커버링 발생 가능성이 제기되며 2차 매물대 돌파 및 추석전 25층 기대.</t>
+          <t>가온전선과의 비교 및 저평가 해소 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['숏커버링', '매물대', '수익률']</t>
+          <t>['가온전선', '저평가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31250</v>
+        <v>6470</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.21%</t>
+          <t>'+10.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="H6" t="n">
-        <v>11.44</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28100</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>11.46</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>231541000000</v>
+        <v>96409368685</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>728000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 및 저평가 해소 기대.</t>
+          <t>매출액 및 영업이익 예상 기반 긍정적 전망, 외국인 투자자 매수.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['가온전선', '저평가']</t>
+          <t>['매출액', '영업이익', '외국인 투자']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,130 +1016,130 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8020</v>
+        <v>12590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.16%</t>
+          <t>'+8.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
-        <v>444</v>
+        <v>792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7280</v>
+        <v>11580</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13820</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="N7" t="n">
-        <v>0.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>160264000000</v>
+        <v>130557373545</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>21150</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8140</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>276000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
+          <t>개인 손실 및 외인/기관 매매 방식에 대한 혼재된 의견.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공시', '외국인 매수', '급락 우려']</t>
+          <t>['외인 매매', '손실', '의견']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12540</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.95%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>808</v>
+        <v>224</v>
       </c>
       <c r="H8" t="n">
-        <v>8.029999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,222 +1147,222 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11510</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.699999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>129225000000</v>
+        <v>158827865795</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양극단 의견 속에서 일부 손실 경험 후 매도. 셀그램 관련 뉴스 기대감 및 외인/기관 동시 매수 언급이 있으나, 주가 상승에 대한 불확실성도 공존.</t>
+          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['셀그램', '외인', '기관']</t>
+          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13890</v>
+        <v>14210</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.77%</t>
+          <t>'+6.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="H9" t="n">
-        <v>2.83</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12770</v>
+        <v>13340</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>13480</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>16330</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>13210</v>
       </c>
       <c r="N9" t="n">
-        <v>2.83</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>157185000000</v>
+        <v>213398588055</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>25700</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-108000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
+          <t>주가 조작 의혹 및 종목에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
+          <t>['주가 조작', '부정적 평가', '잡주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4125</v>
+        <v>1839000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.42%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>247</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>137</v>
+        <v>492</v>
       </c>
       <c r="G10" t="n">
-        <v>916</v>
+        <v>2485</v>
       </c>
       <c r="H10" t="n">
-        <v>0.55</v>
+        <v>50.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3840</v>
+        <v>1745000</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1810000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1852000</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1805000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.95</v>
+        <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>42854000000</v>
+        <v>5098247928000</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미투온 계열사 미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재 언급. 스테이블코인 테마 편입 가능성과 함께 시총 1500억 기준 매수 기회 언급. 주포 물량 넘김 경고도 존재.</t>
+          <t>자사주 매입 및 차익 실현 관련 언급, 목표가 상향 조정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['STO', '코인', '스테이블코인']</t>
+          <t>['자사주 매입', '목표가', '차익 실현']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13860</v>
+        <v>13870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+7.36%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1423,34 +1423,34 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>12910</v>
+        <v>13330</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>13210</v>
       </c>
       <c r="N11" t="n">
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>74416000000</v>
+        <v>75688006945</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1847000</v>
+        <v>18470</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.12%</t>
+          <t>'+3.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>195</v>
       </c>
       <c r="F12" t="n">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>2478</v>
+        <v>435</v>
       </c>
       <c r="H12" t="n">
-        <v>50.1</v>
+        <v>0.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1757000</v>
+        <v>17930</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>17260</v>
       </c>
       <c r="N12" t="n">
-        <v>50.2</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>4983385000000</v>
+        <v>89967055155</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>185/200/220 등 구체적인 목표 주가 언급과 함께 자사주 매입 및 쌍끌이 매수세 확인. 다음 주 전망 및 200만/400만원 목표 조정에 대한 기대감이 나타남.</t>
+          <t>락업 해제 및 프로그램 매매 관련 불확실성, 목표가 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주', '목표주가', '매수세']</t>
+          <t>['락업 해제', '프로그램 매매', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52400</v>
+        <v>259750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+2.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>180</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>433</v>
       </c>
       <c r="G13" t="n">
-        <v>521</v>
+        <v>1968</v>
       </c>
       <c r="H13" t="n">
-        <v>38.54</v>
+        <v>46.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50200</v>
+        <v>252500</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>262000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N13" t="n">
-        <v>38.62</v>
+        <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>255341000000</v>
+        <v>2861436735250</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-1533000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>968000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>52000~53000원 돌파 기대감 및 외인/기관의 매수세 언급. 4분기 예상 수주액 5조원 이상 전망치가 제시되었으며, 공매도 누르고 개인 털어내는 작업으로 해석.</t>
+          <t>대통령 기자회견 관련 내용으로, 종목 분석과는 무관한 정치적 언급이 주를 이룸. ETF 상폐에 대한 언급도 있으나 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '외인', '기관']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,18 +1660,18 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86400</v>
+        <v>10900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>313</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>1363</v>
+        <v>215</v>
       </c>
       <c r="H14" t="n">
-        <v>23.23</v>
+        <v>12.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>84100</v>
+        <v>10610</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10730</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>12390</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>10510</v>
       </c>
       <c r="N14" t="n">
-        <v>23.27</v>
+        <v>12.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>120459043365</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '대미 투자', '수주']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>260000</v>
+        <v>10510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.56%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>137</v>
       </c>
       <c r="F15" t="n">
-        <v>433</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>1957</v>
+        <v>233</v>
       </c>
       <c r="H15" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>253500</v>
+        <v>10250</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10280</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>10230</v>
       </c>
       <c r="N15" t="n">
-        <v>46.52</v>
+        <v>18.42</v>
       </c>
       <c r="O15" t="n">
-        <v>2814732000000</v>
+        <v>213495123835</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>22450</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대통령 기자회견 관련 내용으로, 종목 분석과는 무관한 정치적 언급이 주를 이룸. ETF 상폐에 대한 언급도 있으나 구체적인 근거는 부족.</t>
+          <t>주가 조작 의혹 및 광통신 주 관련 불확실한 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['주가 조작', '광통신', '전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14200</v>
+        <v>18910</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.75</v>
+        <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="F16" t="n">
         <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>154</v>
+        <v>518</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>10.74</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13910</v>
+        <v>18490</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>18760</v>
       </c>
       <c r="N16" t="n">
-        <v>1.76</v>
+        <v>10.85</v>
       </c>
       <c r="O16" t="n">
-        <v>211789000000</v>
+        <v>140082821195</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>개잡주로 평가하며 대광으로 이동 권유. 주가 조작 의혹 제기 및 하락 조정 예상. 13000원, 18000원 돌파 예측은 있었으나, 매도 후 후발주 가능성도 언급.</t>
+          <t>미국 증시 및 중동 전쟁 관련 이슈 속에서 대차해지 운동 동참 독려. 5조원대 투르크 수자원 시장 건 수주 관련 언급이 있으나, 주가 하락에 대한 불만도 제기됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '후발주', '하락조정']</t>
+          <t>['대차해지', '수주', '중동']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,251 +1936,251 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17460</v>
+        <v>52000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.99%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G17" t="n">
-        <v>201</v>
+        <v>534</v>
       </c>
       <c r="H17" t="n">
-        <v>0.97</v>
+        <v>38.54</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17120</v>
+        <v>51100</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>51600</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>55200</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>38.62</v>
       </c>
       <c r="O17" t="n">
-        <v>88473000000</v>
+        <v>264921763200</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
+          <t>수주 예상액 기반 긍정적 전망 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
+          <t>['수주', '공매도', '전망']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18940</v>
+        <v>17540</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.77%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>0.27</v>
       </c>
       <c r="E18" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>514</v>
+        <v>205</v>
       </c>
       <c r="H18" t="n">
-        <v>10.74</v>
+        <v>0.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18610</v>
+        <v>17250</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>17920</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>18440</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>17430</v>
       </c>
       <c r="N18" t="n">
-        <v>10.85</v>
+        <v>0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>137804000000</v>
+        <v>89491634125</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 및 중동 전쟁 관련 이슈 속에서 대차해지 운동 동참 독려. 5조원대 투르크 수자원 시장 건 수주 관련 언급이 있으나, 주가 하락에 대한 불만도 제기됨.</t>
+          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '수주', '중동']</t>
+          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10125</v>
+        <v>4100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.25%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="H19" t="n">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10150</v>
+        <v>4095</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4095</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>0.87</v>
       </c>
       <c r="O19" t="n">
-        <v>37141000000</v>
+        <v>76848926709</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10560</v>
+        <v>13350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>437</v>
       </c>
       <c r="H20" t="n">
-        <v>18.13</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10590</v>
+        <v>13360</v>
       </c>
       <c r="K20" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14450</v>
+      </c>
+      <c r="M20" t="n">
+        <v>13280</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>18.42</v>
-      </c>
       <c r="O20" t="n">
-        <v>211885000000</v>
+        <v>43139589990</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-88000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 차익 실현 매도 의견 혼재.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인', '차익 실현']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10920</v>
+        <v>85100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.44%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>314</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>1387</v>
       </c>
       <c r="H21" t="n">
-        <v>12.5</v>
+        <v>23.23</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>11080</v>
+        <v>85400</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>87800</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="N21" t="n">
-        <v>12.6</v>
+        <v>23.27</v>
       </c>
       <c r="O21" t="n">
-        <v>119810000000</v>
+        <v>151108336750</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-476000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['원전', '대미 투자', '수주']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13360</v>
+        <v>10070</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-4.10%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>430</v>
+        <v>251</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13740</v>
+        <v>10500</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10710</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>42807000000</v>
+        <v>37697099825</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>15960</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-114000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4115</v>
+        <v>4210</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.01%</t>
+          <t>'-9.17%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.14</v>
+        <v>-0.4</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>257</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="G23" t="n">
-        <v>227</v>
+        <v>938</v>
       </c>
       <c r="H23" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4425</v>
+        <v>4635</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4465</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4535</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4065</v>
       </c>
       <c r="N23" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="O23" t="n">
-        <v>76062000000</v>
+        <v>45619075258</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-108000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>미투온 계열사 미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재 언급. 스테이블코인 테마 편입 가능성과 함께 시총 1500억 기준 매수 기회 언급. 주포 물량 넘김 경고도 존재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['STO', '코인', '스테이블코인']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -2595,20 +2595,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-64.29%</t>
+          <t>'-53.49%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.02</v>
       </c>
       <c r="E24" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H24" t="n">
         <v>3.69</v>
@@ -2619,31 +2619,31 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N24" t="n">
         <v>3.71</v>
       </c>
       <c r="O24" t="n">
-        <v>227000000</v>
+        <v>226701565</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260918_15.xlsx
+++ b/data/trending_integrated_20260918_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26550</v>
+        <v>26800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.92%</t>
+          <t>'+24.07%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F2" t="n">
         <v>168</v>
       </c>
       <c r="G2" t="n">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>475648847075</v>
+        <v>493102722275</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4만원-5만원대 움직임 언급 및 5~6만원대 재진입 신호 기대. 통신주 하락 속에서 성호전자 미래 성장성 및 프로그램 폭풍 매수에 대한 긍정적 전망 제시.</t>
+          <t>자회사 나스닥 상장 추진에 따른 기업 가치 재평가 기대감과 프로그램 매수 동향.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['성장성', '프로그램매수', '통신주']</t>
+          <t>['나스닥 상장', '기업가치', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8030</v>
+        <v>8080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.39%</t>
+          <t>'+15.10%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>161168879530</v>
+        <v>161774887610</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18140</v>
+        <v>18320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.46%</t>
+          <t>'+13.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F4" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G4" t="n">
-        <v>2776</v>
+        <v>2859</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>893245605160</v>
+        <v>958723941560</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31300</v>
+        <v>31450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.60%</t>
+          <t>'+11.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>234060480650</v>
+        <v>245807212900</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6470</v>
+        <v>6500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.03%</t>
+          <t>'+10.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H6" t="n">
         <v>2.85</v>
@@ -978,7 +978,7 @@
         <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>96409368685</v>
+        <v>97031483685</v>
       </c>
       <c r="P6" t="n">
         <v>11760</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>매출액 및 영업이익 예상 기반 긍정적 전망, 외국인 투자자 매수.</t>
+          <t>향후 매출 및 영업이익 전망과 함께 박스권 돌파 및 외인 매수 동향에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매출액', '영업이익', '외국인 투자']</t>
+          <t>['매출', '영업이익', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12590</v>
+        <v>12530</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.72%</t>
+          <t>'+8.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F7" t="n">
         <v>106</v>
       </c>
       <c r="G7" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="H7" t="n">
         <v>8.029999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>130557373545</v>
+        <v>131469219235</v>
       </c>
       <c r="P7" t="n">
         <v>21150</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>개인 손실 및 외인/기관 매매 방식에 대한 혼재된 의견.</t>
+          <t>매매 경험 공유와 함께 단기적 손실 및 외인/기관 매매 동향에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인 매매', '손실', '의견']</t>
+          <t>['외인', '기관', '손실']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>13890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.78%</t>
+          <t>'+8.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
         <v>52</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>158827865795</v>
+        <v>159509461985</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14210</v>
+        <v>14250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.52%</t>
+          <t>'+6.82%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.75</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H9" t="n">
         <v>1.01</v>
@@ -1254,7 +1254,7 @@
         <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>213398588055</v>
+        <v>213943949805</v>
       </c>
       <c r="P9" t="n">
         <v>25700</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 종목에 대한 부정적 평가.</t>
+          <t>주가 조작 의혹과 함께 투자 경고 및 단기 고점 논란에 대한 부정적 의견.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '부정적 평가', '잡주']</t>
+          <t>['주가 조작', '투자 경고', '단기 고점']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1839000</v>
+        <v>1857000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+6.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G10" t="n">
-        <v>2485</v>
+        <v>2501</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1337,7 +1337,7 @@
         <v>1810000</v>
       </c>
       <c r="L10" t="n">
-        <v>1852000</v>
+        <v>1857000</v>
       </c>
       <c r="M10" t="n">
         <v>1805000</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>5098247928000</v>
+        <v>7986432600000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>자사주 매입 및 차익 실현 관련 언급, 목표가 상향 조정.</t>
+          <t>주가 상승 기대감과 함께 자사주 매수, 쌍끌이 매수 동향에 대한 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주 매입', '목표가', '차익 실현']</t>
+          <t>['자사주', '매수', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>75688006945</v>
+        <v>76957763835</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18470</v>
+        <v>261000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="G12" t="n">
-        <v>435</v>
+        <v>1965</v>
       </c>
       <c r="H12" t="n">
-        <v>0.98</v>
+        <v>46.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17930</v>
+        <v>252500</v>
       </c>
       <c r="K12" t="n">
-        <v>18400</v>
+        <v>261000</v>
       </c>
       <c r="L12" t="n">
-        <v>20400</v>
+        <v>262000</v>
       </c>
       <c r="M12" t="n">
-        <v>17260</v>
+        <v>257500</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>89967055155</v>
+        <v>3814117272250</v>
       </c>
       <c r="P12" t="n">
-        <v>21100</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>9900</v>
+        <v>78600</v>
       </c>
       <c r="R12" t="n">
-        <v>43000</v>
+        <v>-1533000</v>
       </c>
       <c r="S12" t="n">
-        <v>-1000</v>
+        <v>968000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>락업 해제 및 프로그램 매매 관련 불확실성, 목표가 제시.</t>
+          <t>정치적 발언에 대한 논란과 ETF 상장 폐지 질문이 혼재된 내용.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['락업 해제', '프로그램 매매', '목표가']</t>
+          <t>['기자회견', 'ETF', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>259750</v>
+        <v>18470</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+3.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>199</v>
       </c>
       <c r="F13" t="n">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>1968</v>
+        <v>444</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>0.98</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>17930</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>18400</v>
       </c>
       <c r="L13" t="n">
-        <v>262000</v>
+        <v>20400</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>17260</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2861436735250</v>
+        <v>90306108945</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>21100</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>9900</v>
       </c>
       <c r="R13" t="n">
-        <v>-1533000</v>
+        <v>43000</v>
       </c>
       <c r="S13" t="n">
-        <v>968000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대통령 기자회견 관련 내용으로, 종목 분석과는 무관한 정치적 언급이 주를 이룸. ETF 상폐에 대한 언급도 있으나 구체적인 근거는 부족.</t>
+          <t>락업 해제 및 프로그램 매매 관련 불확실성, 목표가 제시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['락업 해제', '프로그램 매매', '목표가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10900</v>
+        <v>10520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.63%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>-0.29</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="H14" t="n">
-        <v>12.5</v>
+        <v>18.13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10610</v>
+        <v>10250</v>
       </c>
       <c r="K14" t="n">
-        <v>10730</v>
+        <v>10280</v>
       </c>
       <c r="L14" t="n">
-        <v>12390</v>
+        <v>11500</v>
       </c>
       <c r="M14" t="n">
-        <v>10510</v>
+        <v>10230</v>
       </c>
       <c r="N14" t="n">
-        <v>12.6</v>
+        <v>18.42</v>
       </c>
       <c r="O14" t="n">
-        <v>120459043365</v>
+        <v>214185961715</v>
       </c>
       <c r="P14" t="n">
-        <v>14350</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>465</v>
+        <v>1760</v>
       </c>
       <c r="R14" t="n">
-        <v>74000</v>
+        <v>-55000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>주가 조작 의혹 및 광통신 주 관련 불확실한 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['주가 조작', '광통신', '전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10510</v>
+        <v>18910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>233</v>
+        <v>527</v>
       </c>
       <c r="H15" t="n">
-        <v>18.13</v>
+        <v>10.74</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10250</v>
+        <v>18490</v>
       </c>
       <c r="K15" t="n">
-        <v>10280</v>
+        <v>18900</v>
       </c>
       <c r="L15" t="n">
-        <v>11500</v>
+        <v>19700</v>
       </c>
       <c r="M15" t="n">
-        <v>10230</v>
+        <v>18760</v>
       </c>
       <c r="N15" t="n">
-        <v>18.42</v>
+        <v>10.85</v>
       </c>
       <c r="O15" t="n">
-        <v>213495123835</v>
+        <v>146586386215</v>
       </c>
       <c r="P15" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-55000</v>
+        <v>350000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>135000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 광통신 주 관련 불확실한 전망.</t>
+          <t>미국 증시 및 중동 전쟁 관련 이슈 속에서 대차해지 운동 동참 독려. 5조원대 투르크 수자원 시장 건 수주 관련 언급이 있으나, 주가 하락에 대한 불만도 제기됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 조작', '광통신', '전망']</t>
+          <t>['대차해지', '수주', '중동']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18910</v>
+        <v>10850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.26%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>518</v>
+        <v>222</v>
       </c>
       <c r="H16" t="n">
-        <v>10.74</v>
+        <v>12.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,244 +1883,244 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18490</v>
+        <v>10610</v>
       </c>
       <c r="K16" t="n">
-        <v>18900</v>
+        <v>10730</v>
       </c>
       <c r="L16" t="n">
-        <v>19700</v>
+        <v>12390</v>
       </c>
       <c r="M16" t="n">
-        <v>18760</v>
+        <v>10510</v>
       </c>
       <c r="N16" t="n">
-        <v>10.85</v>
+        <v>12.6</v>
       </c>
       <c r="O16" t="n">
-        <v>140082821195</v>
+        <v>120770611965</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>14350</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>465</v>
       </c>
       <c r="R16" t="n">
-        <v>350000</v>
+        <v>74000</v>
       </c>
       <c r="S16" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 증시 및 중동 전쟁 관련 이슈 속에서 대차해지 운동 동참 독려. 5조원대 투르크 수자원 시장 건 수주 관련 언급이 있으나, 주가 하락에 대한 불만도 제기됨.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '수주', '중동']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52000</v>
+        <v>17570</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>0.27</v>
       </c>
       <c r="E17" t="n">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>534</v>
+        <v>208</v>
       </c>
       <c r="H17" t="n">
-        <v>38.54</v>
+        <v>0.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>51100</v>
+        <v>17250</v>
       </c>
       <c r="K17" t="n">
-        <v>51600</v>
+        <v>17920</v>
       </c>
       <c r="L17" t="n">
-        <v>55200</v>
+        <v>18440</v>
       </c>
       <c r="M17" t="n">
-        <v>51500</v>
+        <v>17430</v>
       </c>
       <c r="N17" t="n">
-        <v>38.62</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>264921763200</v>
+        <v>89975634915</v>
       </c>
       <c r="P17" t="n">
-        <v>67300</v>
+        <v>30550</v>
       </c>
       <c r="Q17" t="n">
-        <v>23150</v>
+        <v>6100</v>
       </c>
       <c r="R17" t="n">
-        <v>447000</v>
+        <v>-97000</v>
       </c>
       <c r="S17" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>수주 예상액 기반 긍정적 전망 및 공매도 관련 언급.</t>
+          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '공매도', '전망']</t>
+          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17540</v>
+        <v>51800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
-        <v>205</v>
+        <v>550</v>
       </c>
       <c r="H18" t="n">
-        <v>0.97</v>
+        <v>38.54</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17250</v>
+        <v>51100</v>
       </c>
       <c r="K18" t="n">
-        <v>17920</v>
+        <v>51600</v>
       </c>
       <c r="L18" t="n">
-        <v>18440</v>
+        <v>55200</v>
       </c>
       <c r="M18" t="n">
-        <v>17430</v>
+        <v>51500</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7</v>
+        <v>38.62</v>
       </c>
       <c r="O18" t="n">
-        <v>89491634125</v>
+        <v>290837251400</v>
       </c>
       <c r="P18" t="n">
-        <v>30550</v>
+        <v>67300</v>
       </c>
       <c r="Q18" t="n">
-        <v>6100</v>
+        <v>23150</v>
       </c>
       <c r="R18" t="n">
-        <v>-97000</v>
+        <v>447000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
+          <t>주가 상승에 대한 기대와 공매도 물량 소화, 그리고 향후 수주 예상액에 대한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
+          <t>['공매도', '수주', '주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-0.14</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
         <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H19" t="n">
         <v>0.73</v>
@@ -2174,7 +2174,7 @@
         <v>0.87</v>
       </c>
       <c r="O19" t="n">
-        <v>76848926709</v>
+        <v>77252924309</v>
       </c>
       <c r="P19" t="n">
         <v>8100</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13350</v>
+        <v>13340</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.15%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>43139589990</v>
+        <v>43289584950</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>호재에도 불구하고 주가 부진에 대한 답답함과 테마주 관련 불확실성에 대한 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['호재', '실적', '테마주']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>85100</v>
+        <v>84900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G21" t="n">
-        <v>1387</v>
+        <v>1427</v>
       </c>
       <c r="H21" t="n">
         <v>23.23</v>
@@ -2352,13 +2352,13 @@
         <v>87800</v>
       </c>
       <c r="M21" t="n">
-        <v>85000</v>
+        <v>84900</v>
       </c>
       <c r="N21" t="n">
         <v>23.27</v>
       </c>
       <c r="O21" t="n">
-        <v>151108336750</v>
+        <v>191739014650</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2424,7 +2424,7 @@
         <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H22" t="n">
         <v>1.24</v>
@@ -2450,7 +2450,7 @@
         <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>37697099825</v>
+        <v>37909888995</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4210</v>
+        <v>4220</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-8.95%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.4</v>
       </c>
       <c r="E23" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F23" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G23" t="n">
-        <v>938</v>
+        <v>956</v>
       </c>
       <c r="H23" t="n">
         <v>0.55</v>
@@ -2542,7 +2542,7 @@
         <v>0.95</v>
       </c>
       <c r="O23" t="n">
-        <v>45619075258</v>
+        <v>46225734018</v>
       </c>
       <c r="P23" t="n">
         <v>6900</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미투온 계열사 미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재 언급. 스테이블코인 테마 편입 가능성과 함께 시총 1500억 기준 매수 기회 언급. 주포 물량 넘김 경고도 존재.</t>
+          <t>STO 사업 추진 및 스테이블 코인 테마 기대와 함께 공매도에 대한 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['STO', '코인', '스테이블코인']</t>
+          <t>['STO', '스테이블 코인', '공매도']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2602,13 +2602,13 @@
         <v>-0.02</v>
       </c>
       <c r="E24" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="H24" t="n">
         <v>3.69</v>
@@ -2634,7 +2634,7 @@
         <v>3.71</v>
       </c>
       <c r="O24" t="n">
-        <v>226701565</v>
+        <v>252699685</v>
       </c>
       <c r="P24" t="n">
         <v>901</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>K-OTC 거래 및 대주주 변경 관련 언급이 있으나, 회사의 신뢰성에 대한 의문과 함께 주가 하락 및 장외 거래 가능성에 대한 부정적인 의견이 지배적. '10원도 비싸다'는 의견도 있음.</t>
+          <t>K-OTC 거래 및 대주주 관련 내용이 있으나, 주가 하락 및 부정적 감정 표현이 주를 이룸.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['K-OTC', '대주주', '장외거래']</t>
+          <t>['K-OTC', '대주주', '주가 하락']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260918_15.xlsx
+++ b/data/trending_integrated_20260918_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F2" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G2" t="n">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>493102722275</v>
+        <v>493522758675</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 추진에 따른 기업 가치 재평가 기대감과 프로그램 매수 동향.</t>
+          <t>성호전자 자회사 나스닥 상장 추진에 따른 기업가치 재평가 기대. 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['나스닥 상장', '기업가치', '프로그램 매수']</t>
+          <t>['성호전자', '기업가치 재평가', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>161774887610</v>
+        <v>161813283770</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -762,13 +762,13 @@
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F4" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G4" t="n">
-        <v>2859</v>
+        <v>2904</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>958723941560</v>
+        <v>959023418600</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>수익률 520% 돌파 및 18000/20000원 돌파 기대감. 코닝, 어플라이드옵토 등 관련주 상승 언급과 함께 숏커버링 발생 가능성이 제기되며 2차 매물대 돌파 및 추석전 25층 기대.</t>
+          <t>대한광통신 주가 급등 및 숏커버링 발생. 외인/기관/투신 동시 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['숏커버링', '매물대', '수익률']</t>
+          <t>['대한광통신', '주가 급등', '숏커버링']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
         <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>245807212900</v>
+        <v>245927760750</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -946,13 +946,13 @@
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F6" t="n">
         <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
         <v>2.85</v>
@@ -978,7 +978,7 @@
         <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>97031483685</v>
+        <v>97051035685</v>
       </c>
       <c r="P6" t="n">
         <v>11760</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>향후 매출 및 영업이익 전망과 함께 박스권 돌파 및 외인 매수 동향에 대한 언급.</t>
+          <t>KBI메탈 박스권 돌파 및 실적 전망 호조. 전환사채 발행 가능성 언급. 외국인/프로그램 매수 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매출', '영업이익', '외인 매수']</t>
+          <t>['KBI메탈', '박스권 돌파', '실적 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="H7" t="n">
         <v>8.029999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>131469219235</v>
+        <v>131474707375</v>
       </c>
       <c r="P7" t="n">
         <v>21150</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매매 경험 공유와 함께 단기적 손실 및 외인/기관 매매 동향에 대한 언급.</t>
+          <t>파미셀 주가 하락 및 개인 손실 발생. 외인/기관 동시 매수세 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인', '기관', '손실']</t>
+          <t>['파미셀', '주가 하락', '손실']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>159509461985</v>
+        <v>159559132625</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1222,13 +1222,13 @@
         <v>-0.75</v>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H9" t="n">
         <v>1.01</v>
@@ -1254,7 +1254,7 @@
         <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>213943949805</v>
+        <v>213995691555</v>
       </c>
       <c r="P9" t="n">
         <v>25700</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 의혹과 함께 투자 경고 및 단기 고점 논란에 대한 부정적 의견.</t>
+          <t>빛샘전자 주가 급등에 대한 부정적 시각 및 주가 조작 의혹 제기. 경고/정지 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '투자 경고', '단기 고점']</t>
+          <t>['빛샘전자', '주가 조작', '부정적 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1320,7 +1320,7 @@
         <v>487</v>
       </c>
       <c r="G10" t="n">
-        <v>2501</v>
+        <v>2589</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>7986432600000</v>
+        <v>8005125162000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 상승 기대감과 함께 자사주 매수, 쌍끌이 매수 동향에 대한 언급.</t>
+          <t>SK하이닉스 주가 상승에 대한 강한 기대감. 외인 대규모 매수 및 목표가 상향 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주', '매수', '주가']</t>
+          <t>['SK하이닉스', '외인 매수', '목표가 상향']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>76957763835</v>
+        <v>77035241655</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G12" t="n">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="H12" t="n">
         <v>46.48</v>
@@ -1530,7 +1530,7 @@
         <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>3814117272250</v>
+        <v>3815188155250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 발언에 대한 논란과 ETF 상장 폐지 질문이 혼재된 내용.</t>
+          <t>삼성전자 주가 상승에 대한 기대감 속 정치적 이슈 언급. 대규모 매수세 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['기자회견', 'ETF', '정치']</t>
+          <t>['삼성전자', '대규모 매수', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.38</v>
       </c>
       <c r="E13" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="H13" t="n">
         <v>0.98</v>
@@ -1622,7 +1622,7 @@
         <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>90306108945</v>
+        <v>90313441535</v>
       </c>
       <c r="P13" t="n">
         <v>21100</v>
@@ -1682,13 +1682,13 @@
         <v>-0.29</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F14" t="n">
         <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H14" t="n">
         <v>18.13</v>
@@ -1714,7 +1714,7 @@
         <v>18.42</v>
       </c>
       <c r="O14" t="n">
-        <v>214185961715</v>
+        <v>214248650395</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 광통신 주 관련 불확실한 전망.</t>
+          <t>광통신주에 대한 부정적 전망 및 주가 조작 의혹 제기. 외인 매도세 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '광통신', '전망']</t>
+          <t>['광통신주', '주가 조작', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="H15" t="n">
         <v>10.74</v>
@@ -1806,7 +1806,7 @@
         <v>10.85</v>
       </c>
       <c r="O15" t="n">
-        <v>146586386215</v>
+        <v>146661194175</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1866,10 +1866,10 @@
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
         <v>222</v>
@@ -1898,7 +1898,7 @@
         <v>12.6</v>
       </c>
       <c r="O16" t="n">
-        <v>120770611965</v>
+        <v>120804778615</v>
       </c>
       <c r="P16" t="n">
         <v>14350</v>
@@ -1958,13 +1958,13 @@
         <v>0.27</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H17" t="n">
         <v>0.97</v>
@@ -1990,7 +1990,7 @@
         <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>89975634915</v>
+        <v>90005029525</v>
       </c>
       <c r="P17" t="n">
         <v>30550</v>
@@ -2050,13 +2050,13 @@
         <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="H18" t="n">
         <v>38.54</v>
@@ -2082,7 +2082,7 @@
         <v>38.62</v>
       </c>
       <c r="O18" t="n">
-        <v>290837251400</v>
+        <v>290874288400</v>
       </c>
       <c r="P18" t="n">
         <v>67300</v>
@@ -2127,215 +2127,215 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4100</v>
+        <v>8400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>236</v>
+        <v>435</v>
       </c>
       <c r="H19" t="n">
-        <v>0.73</v>
+        <v>26.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4095</v>
+        <v>8380</v>
       </c>
       <c r="K19" t="n">
-        <v>4200</v>
+        <v>8480</v>
       </c>
       <c r="L19" t="n">
-        <v>4400</v>
+        <v>8590</v>
       </c>
       <c r="M19" t="n">
-        <v>4095</v>
+        <v>8350</v>
       </c>
       <c r="N19" t="n">
-        <v>0.87</v>
+        <v>26.54</v>
       </c>
       <c r="O19" t="n">
-        <v>77252924309</v>
+        <v>32336896265</v>
       </c>
       <c r="P19" t="n">
-        <v>8100</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>592</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-431000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>LG디스플레이 주가 부진 및 정부 지원 정책에 대한 부정적 전망. 외인 매도 및 개인 매수 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['LG디스플레이', '주가 부진', '외인 매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13340</v>
+        <v>4100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.15%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>101</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>247</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4200</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4400</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O20" t="n">
+        <v>77307331309</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>592</v>
+      </c>
+      <c r="R20" t="n">
         <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>122</v>
-      </c>
-      <c r="F20" t="n">
-        <v>77</v>
-      </c>
-      <c r="G20" t="n">
-        <v>453</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>13360</v>
-      </c>
-      <c r="K20" t="n">
-        <v>13450</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14450</v>
-      </c>
-      <c r="M20" t="n">
-        <v>13280</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>43289584950</v>
-      </c>
-      <c r="P20" t="n">
-        <v>19380</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-88000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호재에도 불구하고 주가 부진에 대한 답답함과 테마주 관련 불확실성에 대한 언급.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호재', '실적', '테마주']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84900</v>
+        <v>13340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>122</v>
       </c>
       <c r="F21" t="n">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>1427</v>
+        <v>456</v>
       </c>
       <c r="H21" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K21" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L21" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M21" t="n">
-        <v>84900</v>
+        <v>13280</v>
       </c>
       <c r="N21" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>191739014650</v>
+        <v>43305486230</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-476000</v>
+        <v>-88000</v>
       </c>
       <c r="S21" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
+          <t>금호건설, 호남 반도체 및 송도 세브란스병원 관련 기대감 언급되나 구체적 호재 부재. 단기 급등 및 하락에 대한 상반된 전망 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '대미 투자', '수주']</t>
+          <t>['호남 반도체', '송도 세브란스병원', '실적']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10070</v>
+        <v>84900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.10%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>332</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
-        <v>252</v>
+        <v>1448</v>
       </c>
       <c r="H22" t="n">
-        <v>1.24</v>
+        <v>23.23</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,183 +2435,183 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10500</v>
+        <v>85400</v>
       </c>
       <c r="K22" t="n">
-        <v>10650</v>
+        <v>87300</v>
       </c>
       <c r="L22" t="n">
-        <v>10710</v>
+        <v>87800</v>
       </c>
       <c r="M22" t="n">
-        <v>10030</v>
+        <v>84900</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>23.27</v>
       </c>
       <c r="O22" t="n">
-        <v>37909888995</v>
+        <v>191780360950</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>139200</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>57000</v>
       </c>
       <c r="R22" t="n">
-        <v>-114000</v>
+        <v>-476000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['원전', '대미 투자', '수주']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4220</v>
+        <v>10070</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.95%</t>
+          <t>'-4.10%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="E23" t="n">
-        <v>264</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>956</v>
+        <v>255</v>
       </c>
       <c r="H23" t="n">
-        <v>0.55</v>
+        <v>1.24</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4635</v>
+        <v>10500</v>
       </c>
       <c r="K23" t="n">
-        <v>4465</v>
+        <v>10650</v>
       </c>
       <c r="L23" t="n">
-        <v>4535</v>
+        <v>10710</v>
       </c>
       <c r="M23" t="n">
-        <v>4065</v>
+        <v>10030</v>
       </c>
       <c r="N23" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>46225734018</v>
+        <v>37914913925</v>
       </c>
       <c r="P23" t="n">
-        <v>6900</v>
+        <v>15960</v>
       </c>
       <c r="Q23" t="n">
-        <v>1738</v>
+        <v>3500</v>
       </c>
       <c r="R23" t="n">
-        <v>-108000</v>
+        <v>-114000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 스테이블 코인 테마 기대와 함께 공매도에 대한 우려.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['STO', '스테이블 코인', '공매도']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>4220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-53.49%</t>
+          <t>'-8.95%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.02</v>
+        <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="G24" t="n">
-        <v>166</v>
+        <v>966</v>
       </c>
       <c r="H24" t="n">
-        <v>3.69</v>
+        <v>0.55</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,58 +2619,150 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>43</v>
+        <v>4635</v>
       </c>
       <c r="K24" t="n">
-        <v>44</v>
+        <v>4465</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>4535</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>4065</v>
       </c>
       <c r="N24" t="n">
-        <v>3.71</v>
+        <v>0.95</v>
       </c>
       <c r="O24" t="n">
-        <v>252699685</v>
+        <v>46304732418</v>
       </c>
       <c r="P24" t="n">
-        <v>901</v>
+        <v>6900</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>1738</v>
       </c>
       <c r="R24" t="n">
-        <v>-58000</v>
+        <v>-108000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>K-OTC 거래 및 대주주 관련 내용이 있으나, 주가 하락 및 부정적 감정 표현이 주를 이룸.</t>
+          <t>미투온 계열사 STO 사업 추진 및 암호화폐 관련 호재 기대. 주포 물량 넘김 확인.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['미투온', 'STO 사업', '암호화폐']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'-53.49%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E25" t="n">
+        <v>134</v>
+      </c>
+      <c r="F25" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" t="n">
+        <v>172</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>43</v>
+      </c>
+      <c r="K25" t="n">
+        <v>44</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O25" t="n">
+        <v>253954565</v>
+      </c>
+      <c r="P25" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>20</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="S25" t="n">
         <v>0</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>K-OTC 거래 및 대주주 관련 내용이 있으나, 주가 하락 및 부정적 감정 표현이 주를 이룸.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>['K-OTC', '대주주', '주가 하락']</t>
         </is>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>008290</t>
         </is>
